--- a/data/trans_camb/IP22_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 18,91</t>
+          <t>0,3; 18,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 14,42</t>
+          <t>-4,97; 15,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 33,6</t>
+          <t>-7,64; 32,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 25,43</t>
+          <t>4,42; 26,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 5,11</t>
+          <t>-12,51; 5,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 15,29</t>
+          <t>-7,75; 14,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 19,22</t>
+          <t>5,37; 19,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 6,77</t>
+          <t>-6,55; 6,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 19,12</t>
+          <t>-3,89; 17,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 208,04</t>
+          <t>-1,49; 216,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 167,1</t>
+          <t>-30,47; 171,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 435,88</t>
+          <t>-51,92; 356,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 236,82</t>
+          <t>20,67; 246,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 52,14</t>
+          <t>-65,05; 53,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 137,02</t>
+          <t>-43,86; 125,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,3; 168,55</t>
+          <t>27,01; 174,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 57,46</t>
+          <t>-37,41; 58,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 167,85</t>
+          <t>-24,87; 145,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,98</t>
+          <t>-2,49; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 0,38</t>
+          <t>-8,18; 0,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -2,99</t>
+          <t>-11,69; -2,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,02</t>
+          <t>1,97; 10,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -1,07</t>
+          <t>-8,79; -0,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -2,93</t>
+          <t>-11,81; -3,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,61</t>
+          <t>0,92; 7,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -1,61</t>
+          <t>-7,41; -1,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -4,37</t>
+          <t>-10,45; -4,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 37,77</t>
+          <t>-10,53; 35,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 2,44</t>
+          <t>-34,43; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -15,94</t>
+          <t>-51,43; -14,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 55,98</t>
+          <t>8,05; 55,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,45; -5,1</t>
+          <t>-37,28; -3,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,78; -15,48</t>
+          <t>-49,3; -16,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 37,78</t>
+          <t>4,2; 40,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,78; -8,06</t>
+          <t>-31,89; -7,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,99; -21,59</t>
+          <t>-46,15; -20,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 13,22</t>
+          <t>-0,41; 14,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 7,23</t>
+          <t>-6,34; 6,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 8,87</t>
+          <t>-5,54; 8,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 6,7</t>
+          <t>-8,41; 6,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 0,63</t>
+          <t>-14,55; -0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -0,01</t>
+          <t>-15,52; 0,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 8,08</t>
+          <t>-2,24; 8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,97</t>
+          <t>-7,31; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,8</t>
+          <t>-7,92; 2,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 87,96</t>
+          <t>-3,87; 90,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 47,78</t>
+          <t>-29,08; 46,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 54,7</t>
+          <t>-25,11; 57,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 31,7</t>
+          <t>-28,22; 31,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,57; 4,43</t>
+          <t>-49,52; 0,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -0,35</t>
+          <t>-51,67; 1,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 42,29</t>
+          <t>-9,29; 43,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 10,34</t>
+          <t>-31,17; 13,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 10,44</t>
+          <t>-33,51; 11,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,8</t>
+          <t>0,53; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,81</t>
+          <t>-4,98; 1,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,02</t>
+          <t>-7,58; 0,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,81</t>
+          <t>2,13; 9,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -1,59</t>
+          <t>-8,54; -1,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; -2,8</t>
+          <t>-9,84; -2,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,87</t>
+          <t>2,79; 7,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,94</t>
+          <t>-5,64; -1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -2,48</t>
+          <t>-7,82; -2,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 43,94</t>
+          <t>3,03; 45,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 10,79</t>
+          <t>-23,77; 9,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 0,37</t>
+          <t>-35,79; 2,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 49,21</t>
+          <t>9,8; 47,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,94; -7,87</t>
+          <t>-36,78; -9,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,5; -13,2</t>
+          <t>-41,63; -14,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,34; 40,42</t>
+          <t>12,83; 39,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,15; -4,93</t>
+          <t>-26,05; -5,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,29; -12,73</t>
+          <t>-36,21; -12,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP22_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,86</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,86</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,46</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 18,78</t>
+          <t>4,81; 25,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 15,23</t>
+          <t>-14,05; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 32,11</t>
+          <t>-8,56; 13,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 26,41</t>
+          <t>0,6; 18,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 5,21</t>
+          <t>-4,72; 14,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 14,44</t>
+          <t>-9,68; 8,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 19,99</t>
+          <t>5,2; 19,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,74</t>
+          <t>-6,22; 6,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 17,67</t>
+          <t>-6,1; 8,83</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>101,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-24,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-24,7%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>-6,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 216,7</t>
+          <t>20,07; 220,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 171,82</t>
+          <t>-67,61; 37,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 356,17</t>
+          <t>-46,52; 119,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 246,27</t>
+          <t>0,54; 207,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 53,39</t>
+          <t>-33,53; 152,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 125,73</t>
+          <t>-61,65; 86,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,01; 174,46</t>
+          <t>29,26; 169,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 58,08</t>
+          <t>-36,6; 60,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 145,85</t>
+          <t>-36,64; 72,3</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,87</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-7,64</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,87</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,54</t>
+          <t>-6,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-7,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,71</t>
+          <t>1,53; 11,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,27</t>
+          <t>-8,77; -0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -2,62</t>
+          <t>-11,97; -3,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,79</t>
+          <t>-2,37; 6,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -0,69</t>
+          <t>-7,8; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -3,39</t>
+          <t>-11,3; -2,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,7</t>
+          <t>1,28; 7,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -1,49</t>
+          <t>-7,29; -1,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -4,29</t>
+          <t>-10,27; -4,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-22,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-35,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-18,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-34,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,42%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,73%</t>
+          <t>-33,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,63%</t>
+          <t>-34,37%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 35,04</t>
+          <t>6,52; 56,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 2,22</t>
+          <t>-37,47; -0,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,43; -14,24</t>
+          <t>-49,8; -16,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 55,24</t>
+          <t>-10,22; 36,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,28; -3,4</t>
+          <t>-34,45; 1,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,3; -16,51</t>
+          <t>-48,43; -14,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 40,07</t>
+          <t>5,49; 37,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,89; -7,38</t>
+          <t>-31,9; -7,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -20,96</t>
+          <t>-45,29; -21,4</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,64</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-3,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,13</t>
+          <t>-8,1; 6,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 6,85</t>
+          <t>-14,55; 0,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 8,69</t>
+          <t>-15,65; -0,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 6,78</t>
+          <t>-0,86; 13,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,05</t>
+          <t>-5,99; 7,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 0,16</t>
+          <t>-5,64; 8,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 8,35</t>
+          <t>-2,34; 8,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,34</t>
+          <t>-8,09; 1,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 2,43</t>
+          <t>-8,23; 1,98</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-27,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-32,07%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>33,76%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-27,54%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,28%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-14,67%</t>
+          <t>-15,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 90,23</t>
+          <t>-28,43; 30,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 46,05</t>
+          <t>-49,32; 3,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 57,0</t>
+          <t>-53,47; 3,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 31,98</t>
+          <t>-3,78; 88,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 0,03</t>
+          <t>-26,71; 49,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 1,66</t>
+          <t>-24,89; 53,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 43,93</t>
+          <t>-9,82; 43,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 13,43</t>
+          <t>-33,68; 8,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 11,53</t>
+          <t>-34,5; 10,7</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,72</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-4,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-5,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,88</t>
+          <t>2,1; 9,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,57</t>
+          <t>-8,67; -1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 0,35</t>
+          <t>-10,37; -3,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,43</t>
+          <t>0,78; 7,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -1,81</t>
+          <t>-5,13; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -2,89</t>
+          <t>-7,72; -0,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,73</t>
+          <t>2,6; 7,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -1,12</t>
+          <t>-5,69; -1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; -2,52</t>
+          <t>-7,9; -2,91</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-23,05%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-30,71%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,13%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-8,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-19,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-23,05%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,5%</t>
+          <t>-21,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,95%</t>
+          <t>-26,32%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 45,74</t>
+          <t>8,92; 46,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 9,31</t>
+          <t>-36,83; -9,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 2,12</t>
+          <t>-43,4; -15,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 47,9</t>
+          <t>3,46; 43,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,78; -9,21</t>
+          <t>-24,9; 7,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -14,11</t>
+          <t>-36,3; -3,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,83; 39,41</t>
+          <t>11,8; 40,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -5,69</t>
+          <t>-26,08; -5,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,21; -12,76</t>
+          <t>-36,37; -15,31</t>
         </is>
       </c>
     </row>
